--- a/assets/constructions/examples/ctd_tko_radial_fullround.xlsx
+++ b/assets/constructions/examples/ctd_tko_radial_fullround.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH6"/>
+  <dimension ref="A1:AM6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -599,11 +599,36 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>V11D7993W180T230RVTX</t>
+          <t>V14D7993W157T400R VBX</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -624,7 +649,7 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>V11</t>
+          <t>V14</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -633,25 +658,25 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J2" t="n">
-        <v>6.7</v>
+        <v>9</v>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="P2" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="Q2" t="n">
         <v>-0.03</v>
@@ -660,7 +685,7 @@
         <v>0.03</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9</v>
+        <v>0.785</v>
       </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
@@ -676,7 +701,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>VARGUS_V11</t>
+          <t>VARGUS_V14</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -686,12 +711,12 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>VTX</t>
+          <t>VBX</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>TiAlN</t>
+          <t>TiCN</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
@@ -713,11 +738,30 @@
           <t>2019 / Groovex Catalog</t>
         </is>
       </c>
+      <c r="AI2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>34.05</v>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AL2" t="n">
+        <v>3130.34</v>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>VE08080GR W160T100L VTX</t>
+          <t>V11D7993W300T230RVTX</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -736,43 +780,51 @@
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>V11</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>VARGUS</t>
+        </is>
+      </c>
       <c r="H3" t="n">
+        <v>11</v>
+      </c>
+      <c r="I3" t="n">
         <v>8</v>
       </c>
-      <c r="I3" t="n">
-        <v>6</v>
-      </c>
       <c r="J3" t="n">
-        <v>4.8</v>
+        <v>6.7</v>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="P3" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="R3" t="n">
         <v>0.03</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -782,7 +834,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>VARGUS_V08</t>
+          <t>VARGUS_V11</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -816,14 +868,25 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>2021/Groovex Vargus</t>
+          <t>2019 / Groovex Catalog</t>
+        </is>
+      </c>
+      <c r="AI3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>V14D7993W238T400RVTX</t>
+          <t>V08D7993W120T100RVTX</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -844,7 +907,7 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>V14</t>
+          <t>V08</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -853,25 +916,25 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="I4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J4" t="n">
-        <v>9</v>
+        <v>4.8</v>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>5.6</v>
+        <v>3.6</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>2.38</v>
+        <v>1.2</v>
       </c>
       <c r="Q4" t="n">
         <v>-0.03</v>
@@ -880,7 +943,7 @@
         <v>0.03</v>
       </c>
       <c r="S4" t="n">
-        <v>1.19</v>
+        <v>0.6</v>
       </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
@@ -896,7 +959,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>VARGUS_V14</t>
+          <t>VARGUS_V08</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -933,56 +996,79 @@
           <t>2019 / Groovex Catalog</t>
         </is>
       </c>
+      <c r="AI4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RS11.030R15/AL41F</t>
+          <t>V08D7993W180T100R VBX</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DUEMMEL</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
+          <t>VARGUS</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Mini-V</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>DUE_RS11</t>
+          <t>V08</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>DUEMMEL</t>
+          <t>VARGUS</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J5" t="n">
-        <v>6.7</v>
+        <v>4.8</v>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>3.6</v>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="P5" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q5" t="inlineStr"/>
+        <v>1.8</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-0.03</v>
+      </c>
       <c r="R5" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="S5" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
@@ -998,7 +1084,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>DUEM_RS11</t>
+          <t>VARGUS_V08</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1008,12 +1094,12 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>AL41F</t>
+          <t>VBX</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>TiCN</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
@@ -1032,14 +1118,25 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>2015/Gesamtkatalog_de_en_2015.pdf</t>
+          <t>2019 / Groovex Catalog</t>
+        </is>
+      </c>
+      <c r="AI5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>V14D7993W200T400R VBX</t>
+          <t>VE08080GR W160T100L VTX</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1058,51 +1155,43 @@
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>V14</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>VARGUS</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="I6" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J6" t="n">
-        <v>9</v>
+        <v>4.8</v>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>5.6</v>
+        <v>4.4</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0.03</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1112,7 +1201,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>VARGUS_V14</t>
+          <t>VARGUS_V08</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1122,12 +1211,12 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>VBX</t>
+          <t>VTX</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>TiCN</t>
+          <t>TiAlN</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
@@ -1146,7 +1235,26 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>2019 / Groovex Catalog</t>
+          <t>2021/Groovex Vargus</t>
+        </is>
+      </c>
+      <c r="AI6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AL6" t="n">
+        <v>2629.3</v>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
         </is>
       </c>
     </row>
